--- a/artfynd/A 13760-2022 artfynd.xlsx
+++ b/artfynd/A 13760-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13760-2022 artfynd.xlsx
+++ b/artfynd/A 13760-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3418992</v>
+        <v>132566130</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>102932</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+          <t>Lugnets våtmark, Tullgarn, Vagnhärad, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645252.2480184486</v>
+        <v>645242</v>
       </c>
       <c r="R2" t="n">
-        <v>6539976.248751516</v>
+        <v>6539886</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +764,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-08-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-08-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,74 +790,83 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>källskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Johan Njunjes</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Johan Njunjes</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2702484</v>
+        <v>132566055</v>
       </c>
       <c r="B3" t="n">
-        <v>95709</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>102952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+          <t>Lugnets våtmark, Tullgarn, Vagnhärad, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645252.2480184486</v>
+        <v>645242</v>
       </c>
       <c r="R3" t="n">
-        <v>6539976.248751516</v>
+        <v>6539886</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,27 +890,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-08-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-08-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,24 +916,340 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>källskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2424777</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>645252</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6539976</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>källskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2702484</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>645252</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6539976</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>källskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3418992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>645252</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539976</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>källskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13760-2022 artfynd.xlsx
+++ b/artfynd/A 13760-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132566130</v>
+        <v>135163244</v>
       </c>
       <c r="B2" t="n">
-        <v>57125</v>
+        <v>56945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102932</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,11 +708,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>i par</t>
@@ -720,12 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -764,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,37 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132566055</v>
+        <v>132566130</v>
       </c>
       <c r="B3" t="n">
-        <v>57339</v>
+        <v>57125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102952</v>
+        <v>102932</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -895,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,48 +927,67 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2424777</v>
+        <v>132566055</v>
       </c>
       <c r="B4" t="n">
-        <v>101897</v>
+        <v>57339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220075</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+          <t>Lugnets våtmark, Tullgarn, Vagnhärad, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>645252</v>
+        <v>645242</v>
       </c>
       <c r="R4" t="n">
-        <v>6539976</v>
+        <v>6539886</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,17 +1011,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2002-08-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2002-08-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,53 +1037,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>källskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Johan Njunjes</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Johan Njunjes</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2702484</v>
+        <v>2424777</v>
       </c>
       <c r="B5" t="n">
-        <v>98186</v>
+        <v>101897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>220075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,32 +1160,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3418992</v>
+        <v>2702484</v>
       </c>
       <c r="B6" t="n">
-        <v>106813</v>
+        <v>98186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>220250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1250,6 +1264,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3418992</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad, 400 m NNO om Lilltorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>645252</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539976</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2002-08-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sedd av Hans Rydberg, Källskoginventeringen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>källskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13760-2022 artfynd.xlsx
+++ b/artfynd/A 13760-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135163244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132566130</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132566055</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2424777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2702484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1371,8 +1401,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3418992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 13760-2022 artfynd.xlsx
+++ b/artfynd/A 13760-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135163244</v>
       </c>
       <c r="B2" t="n">
-        <v>56945</v>
+        <v>56950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
